--- a/data/sites/hr/Recruiting and Onboarding/background-check-and-offer-approval-matrix.xlsx
+++ b/data/sites/hr/Recruiting and Onboarding/background-check-and-offer-approval-matrix.xlsx
@@ -7,7 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Architecture" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Controls" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 KPIs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 RACI Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Procedures" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +38,15 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,6 +157,186 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,19 +628,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Background Check and Offer Approval Matrix</t>
+          <t>Background Check and Offer Approval Matrix - Section 1: Executive Summary &amp; Scope</t>
         </is>
       </c>
     </row>
@@ -455,56 +651,46 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 1 (Executive Summary &amp; Scope) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Defines the operational charter, scope boundaries, and executive accountability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 1.1: Standard background checks complete within 3 business days through the vendor portal. Secondary control 1.2: Director-and-above offers require VP of People sign-off before extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Job Level</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Approval Required</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Target SLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Individual Contributor</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Hiring Manager</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3 business days</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Individual Contributor</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hiring Manager + HRBP</t>
+          <t>Hiring Manager</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -516,43 +702,2119 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VP of People</t>
+          <t>Hiring Manager + HRBP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5 business days</t>
+          <t>3 business days</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Executive</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>CEO + VP of People</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>7 business days</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Standard background checks complete within 3 business days through the vendor portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Director-and-above offers require VP of People sign-off before extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 1 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Background Check and Offer Approval Matrix - Section 10: Cross-Functional Dependencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 10 (Cross-Functional Dependencies) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Documents upstream and downstream team dependencies and service-level commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 10.1: Director-and-above offers require VP of People sign-off before extension. Secondary control 10.2: Education verification failures are escalated to the hiring manager and HRBP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Job Level</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Approval Required</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Individual Contributor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 10 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Director-and-above offers require VP of People sign-off before extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Education verification failures are escalated to the hiring manager and HRBP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 10 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Background Check and Offer Approval Matrix - Section 11: Continuous Improvement Roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 11 (Continuous Improvement Roadmap) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 11.1: Education verification failures are escalated to the hiring manager and HRBP. Secondary control 11.2: Offer letters are void if background checks are not cleared within 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Job Level</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Approval Required</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Individual Contributor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 11 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Education verification failures are escalated to the hiring manager and HRBP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Offer letters are void if background checks are not cleared within 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 11 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Background Check and Offer Approval Matrix - Section 12: Appendix, Lineage &amp; Sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Records document lineage, governance metadata, version history, and owner sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 12.1: Offer letters are void if background checks are not cleared within 10 business days. Secondary control 12.2: Standard background checks complete within 3 business days through the vendor portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Job Level</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Approval Required</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Individual Contributor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 12 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Offer letters are void if background checks are not cleared within 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Standard background checks complete within 3 business days through the vendor portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 12 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Background Check and Offer Approval Matrix - Section 2: Architecture &amp; Process Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 2 (Architecture &amp; Process Flow) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Maps end-to-end process stages, handoff gates, and system-of-record integrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 2.1: Director-and-above offers require VP of People sign-off before extension. Secondary control 2.2: Education verification failures are escalated to the hiring manager and HRBP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Job Level</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Approval Required</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Individual Contributor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 2 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Director-and-above offers require VP of People sign-off before extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Education verification failures are escalated to the hiring manager and HRBP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 2 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Background Check and Offer Approval Matrix - Section 3: Governance Standards &amp; Controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 3 (Governance Standards &amp; Controls) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Establishes mandatory compliance controls, approval thresholds, and audit evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 3.1: Education verification failures are escalated to the hiring manager and HRBP. Secondary control 3.2: Offer letters are void if background checks are not cleared within 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Job Level</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Approval Required</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Individual Contributor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 3 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Education verification failures are escalated to the hiring manager and HRBP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Offer letters are void if background checks are not cleared within 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 3 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Background Check and Offer Approval Matrix - Section 4: Operational KPIs &amp; Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 4 (Operational KPIs &amp; Benchmarks) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Tracks baseline performance, target SLAs, and quarterly benchmark progression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 4.1: Offer letters are void if background checks are not cleared within 10 business days. Secondary control 4.2: Standard background checks complete within 3 business days through the vendor portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Job Level</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Approval Required</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Individual Contributor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 4 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Offer letters are void if background checks are not cleared within 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Standard background checks complete within 3 business days through the vendor portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 4 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Background Check and Offer Approval Matrix - Section 5: Roles, Responsibilities &amp; RACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 5 (Roles, Responsibilities &amp; RACI) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Clarifies ownership across accountable executives, operational leads, and reviewers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 5.1: Standard background checks complete within 3 business days through the vendor portal. Secondary control 5.2: Director-and-above offers require VP of People sign-off before extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Job Level</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Approval Required</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Individual Contributor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 5 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Standard background checks complete within 3 business days through the vendor portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Director-and-above offers require VP of People sign-off before extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 5 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Background Check and Offer Approval Matrix - Section 6: Standard Operating Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 6 (Standard Operating Procedures) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Provides step-by-step execution checklists, intake criteria, and verification gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 6.1: Director-and-above offers require VP of People sign-off before extension. Secondary control 6.2: Education verification failures are escalated to the hiring manager and HRBP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Job Level</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Approval Required</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Individual Contributor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 6 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Director-and-above offers require VP of People sign-off before extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Education verification failures are escalated to the hiring manager and HRBP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 6 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Background Check and Offer Approval Matrix - Section 7: Risk Register &amp; Mitigations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 7 (Risk Register &amp; Mitigations) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Catalogs operational, compliance, and delivery risks alongside preventive mitigations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 7.1: Education verification failures are escalated to the hiring manager and HRBP. Secondary control 7.2: Offer letters are void if background checks are not cleared within 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Job Level</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Approval Required</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Individual Contributor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 7 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Education verification failures are escalated to the hiring manager and HRBP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Offer letters are void if background checks are not cleared within 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 7 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Background Check and Offer Approval Matrix - Section 8: Quality Assurance &amp; Audits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 8 (Quality Assurance &amp; Audits) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Specifies sampling frequencies, inspection tolerances, and nonconformance workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 8.1: Offer letters are void if background checks are not cleared within 10 business days. Secondary control 8.2: Standard background checks complete within 3 business days through the vendor portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Job Level</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Approval Required</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Individual Contributor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 8 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Offer letters are void if background checks are not cleared within 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Standard background checks complete within 3 business days through the vendor portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 8 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Background Check and Offer Approval Matrix - Section 9: Exception Handling &amp; Escalations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 9 (Exception Handling &amp; Escalations) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Outlines severity tiers, response SLAs, and cross-functional escalation paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 9.1: Standard background checks complete within 3 business days through the vendor portal. Secondary control 9.2: Director-and-above offers require VP of People sign-off before extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Job Level</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Approval Required</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Target SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Individual Contributor</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hiring Manager + HRBP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VP of People</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO + VP of People</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7 business days</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 9 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Standard background checks complete within 3 business days through the vendor portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Director-and-above offers require VP of People sign-off before extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 9 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/sites/hr/Recruiting and Onboarding/background-check-and-offer-approval-matrix.xlsx
+++ b/data/sites/hr/Recruiting and Onboarding/background-check-and-offer-approval-matrix.xlsx
@@ -13,12 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 KPIs" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 RACI Matrix" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Procedures" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Sign-off" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -220,96 +215,6 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4572000" cy="1524000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4572000" cy="1524000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4572000" cy="1524000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -789,559 +694,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Background Check and Offer Approval Matrix - Section 10: Cross-Functional Dependencies</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 10 (Cross-Functional Dependencies) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Documents upstream and downstream team dependencies and service-level commitments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 10.1: Director-and-above offers require VP of People sign-off before extension. Secondary control 10.2: Education verification failures are escalated to the hiring manager and HRBP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Job Level</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Approval Required</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Target SLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Individual Contributor</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Hiring Manager</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Hiring Manager + HRBP</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>VP of People</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>5 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CEO + VP of People</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sec-10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Hiring Manager + HRBP</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Stage 10 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Director-and-above offers require VP of People sign-off before extension.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Education verification failures are escalated to the hiring manager and HRBP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>• Section 10 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Background Check and Offer Approval Matrix - Section 11: Continuous Improvement Roadmap</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 11 (Continuous Improvement Roadmap) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 11.1: Education verification failures are escalated to the hiring manager and HRBP. Secondary control 11.2: Offer letters are void if background checks are not cleared within 10 business days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Job Level</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Approval Required</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Target SLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Individual Contributor</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Hiring Manager</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Hiring Manager + HRBP</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>VP of People</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>5 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CEO + VP of People</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sec-11</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>VP of People</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Stage 11 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Education verification failures are escalated to the hiring manager and HRBP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Offer letters are void if background checks are not cleared within 10 business days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>• Section 11 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Background Check and Offer Approval Matrix - Section 12: Appendix, Lineage &amp; Sign-off</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Records document lineage, governance metadata, version history, and owner sign-off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 12.1: Offer letters are void if background checks are not cleared within 10 business days. Secondary control 12.2: Standard background checks complete within 3 business days through the vendor portal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Job Level</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Approval Required</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Target SLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Individual Contributor</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Hiring Manager</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Hiring Manager + HRBP</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>VP of People</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>5 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CEO + VP of People</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sec-12</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CEO + VP of People</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Stage 12 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Offer letters are void if background checks are not cleared within 10 business days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Standard background checks complete within 3 business days through the vendor portal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>• Section 12 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2283,7 +1635,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Background Check and Offer Approval Matrix - Section 7: Risk Register &amp; Mitigations</t>
+          <t>Background Check and Offer Approval Matrix - Section 7: Appendix, Lineage &amp; Sign-off</t>
         </is>
       </c>
     </row>
@@ -2297,7 +1649,7 @@
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 7 (Risk Register &amp; Mitigations) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Catalogs operational, compliance, and delivery risks alongside preventive mitigations.</t>
+          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 7 (Appendix, Lineage &amp; Sign-off) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Records document lineage, governance metadata, version history, and owner sign-off.</t>
         </is>
       </c>
     </row>
@@ -2447,374 +1799,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Background Check and Offer Approval Matrix - Section 8: Quality Assurance &amp; Audits</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 8 (Quality Assurance &amp; Audits) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Specifies sampling frequencies, inspection tolerances, and nonconformance workflows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 8.1: Offer letters are void if background checks are not cleared within 10 business days. Secondary control 8.2: Standard background checks complete within 3 business days through the vendor portal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Job Level</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Approval Required</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Target SLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Individual Contributor</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Hiring Manager</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Hiring Manager + HRBP</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>VP of People</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>5 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CEO + VP of People</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sec-8</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CEO + VP of People</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Stage 8 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Offer letters are void if background checks are not cleared within 10 business days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Standard background checks complete within 3 business days through the vendor portal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>• Section 8 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Background Check and Offer Approval Matrix - Section 9: Exception Handling &amp; Escalations</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HR Knowledge Hub | Recruiting and Onboarding | Owner: Priya Natarajan  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Tracks background check vendor SLAs and the approval chain required before an offer can be extended at each job level. Section 9 (Exception Handling &amp; Escalations) applies to Recruiting and Onboarding within HR Knowledge Hub and is maintained by Priya Natarajan. Outlines severity tiers, response SLAs, and cross-functional escalation paths.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 9.1: Standard background checks complete within 3 business days through the vendor portal. Secondary control 9.2: Director-and-above offers require VP of People sign-off before extension.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Job Level</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Approval Required</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Target SLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Individual Contributor</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Hiring Manager</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Hiring Manager + HRBP</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>VP of People</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>5 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CEO + VP of People</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>7 business days</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sec-9</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Hiring Manager</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Stage 9 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Standard background checks complete within 3 business days through the vendor portal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Director-and-above offers require VP of People sign-off before extension.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>• Section 9 review cadence is tracked by Priya Natarajan under Recruiting and Onboarding governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>